--- a/Pruebas calificadas/COLEGIO-ABEL-RODRIGUEZ-CESPEDES-(IED)-301.xlsx_Ajustado_20260624_090455_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-ABEL-RODRIGUEZ-CESPEDES-(IED)-301.xlsx_Ajustado_20260624_090455_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1153,11 +1145,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1348,11 +1336,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1551,11 +1535,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1742,11 +1722,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1941,11 +1917,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2120,11 +2092,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2315,11 +2283,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2518,11 +2482,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2721,11 +2681,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2924,11 +2880,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3127,11 +3079,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3330,11 +3278,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3533,11 +3477,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3736,11 +3676,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3895,11 +3831,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4074,11 +4006,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4277,11 +4205,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4468,11 +4392,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4643,11 +4563,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4846,11 +4762,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5049,11 +4961,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5252,11 +5160,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5455,11 +5359,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5654,11 +5554,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5857,11 +5753,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6056,11 +5948,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6255,11 +6143,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6458,11 +6342,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6661,11 +6541,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6864,11 +6740,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7067,11 +6939,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7270,11 +7138,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7473,11 +7337,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7676,11 +7536,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7879,11 +7735,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8082,11 +7934,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8277,11 +8125,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8480,11 +8324,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8683,11 +8523,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8886,11 +8722,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9085,11 +8917,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9288,11 +9116,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9491,11 +9315,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9694,11 +9514,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9897,11 +9713,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10100,11 +9912,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10303,11 +10111,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10506,11 +10310,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10697,11 +10497,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10900,11 +10696,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11103,11 +10895,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11306,11 +11094,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11509,11 +11293,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11708,11 +11488,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11903,11 +11679,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12106,11 +11878,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12305,11 +12073,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12508,11 +12272,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12711,11 +12471,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12914,11 +12670,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13117,11 +12869,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13320,11 +13068,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13523,11 +13267,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13726,11 +13466,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13929,11 +13665,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -14132,11 +13864,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
